--- a/diseases/d029/2000-2004.xlsx
+++ b/diseases/d029/2000-2004.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -2232,9 +2226,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -3155,9 +3146,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -4078,9 +4066,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -5001,9 +4986,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -5924,9 +5906,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6847,9 +6826,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -7770,9 +7746,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -8693,9 +8666,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -9616,9 +9586,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -10539,9 +10506,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -11462,9 +11426,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -12385,9 +12346,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -12929,9 +12887,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -13556,9 +13511,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -13852,9 +13804,6 @@
       <c r="O73" t="n">
         <v>0</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0</v>
       </c>
@@ -14627,9 +14576,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -14923,9 +14869,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -15698,9 +15641,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -15994,9 +15934,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -16769,9 +16706,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -17065,9 +16999,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -17840,9 +17771,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -18136,9 +18064,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -18911,9 +18836,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -19207,9 +19129,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -19982,9 +19901,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -20278,9 +20194,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -21053,9 +20966,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -21349,9 +21259,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -22124,9 +22031,6 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -22420,9 +22324,6 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
@@ -23195,9 +23096,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -23491,9 +23389,6 @@
       <c r="O127" t="n">
         <v>1</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -24266,9 +24161,6 @@
       <c r="O131" t="n">
         <v>0</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0</v>
       </c>
@@ -24562,9 +24454,6 @@
       <c r="O133" t="n">
         <v>1</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -25337,9 +25226,6 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
@@ -25633,9 +25519,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -26177,9 +26060,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -26573,9 +26453,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -26869,9 +26746,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -27413,9 +27287,6 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
@@ -27709,9 +27580,6 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
@@ -28253,9 +28121,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -28549,9 +28414,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -29093,9 +28955,6 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0</v>
       </c>
@@ -29389,9 +29248,6 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
@@ -29933,9 +29789,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -30229,9 +30082,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -30773,9 +30623,6 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0</v>
       </c>
@@ -31069,9 +30916,6 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0</v>
       </c>
@@ -31613,9 +31457,6 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -31909,9 +31750,6 @@
       <c r="O176" t="n">
         <v>0</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0</v>
       </c>
@@ -32453,9 +32291,6 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -32749,9 +32584,6 @@
       <c r="O181" t="n">
         <v>0</v>
       </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
       <c r="R181" t="n">
         <v>0</v>
       </c>
@@ -33293,9 +33125,6 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
@@ -33589,9 +33418,6 @@
       <c r="O186" t="n">
         <v>0</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0</v>
       </c>
@@ -34133,9 +33959,6 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -34429,9 +34252,6 @@
       <c r="O191" t="n">
         <v>0</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0</v>
       </c>
@@ -34973,9 +34793,6 @@
       <c r="O194" t="n">
         <v>0</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0</v>
       </c>
@@ -35269,9 +35086,6 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0</v>
       </c>
@@ -35813,9 +35627,6 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0</v>
       </c>
@@ -36109,9 +35920,6 @@
       <c r="O201" t="n">
         <v>0</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0</v>
       </c>
@@ -36653,9 +36461,6 @@
       <c r="O204" t="n">
         <v>0</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0</v>
       </c>
@@ -37049,9 +36854,6 @@
       <c r="O206" t="n">
         <v>0</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0</v>
       </c>
@@ -37345,9 +37147,6 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0</v>
       </c>
@@ -37889,9 +37688,6 @@
       <c r="O211" t="n">
         <v>0</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0</v>
       </c>
@@ -38185,9 +37981,6 @@
       <c r="O213" t="n">
         <v>0</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0</v>
       </c>
@@ -38729,9 +38522,6 @@
       <c r="O216" t="n">
         <v>0</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0</v>
       </c>
@@ -39025,9 +38815,6 @@
       <c r="O218" t="n">
         <v>0</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0</v>
       </c>
@@ -39569,9 +39356,6 @@
       <c r="O221" t="n">
         <v>0</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0</v>
       </c>
@@ -39865,9 +39649,6 @@
       <c r="O223" t="n">
         <v>0</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0</v>
       </c>
@@ -40409,9 +40190,6 @@
       <c r="O226" t="n">
         <v>0</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0</v>
       </c>
@@ -40705,9 +40483,6 @@
       <c r="O228" t="n">
         <v>0</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0</v>
       </c>
@@ -41249,9 +41024,6 @@
       <c r="O231" t="n">
         <v>0</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0</v>
       </c>
@@ -41545,9 +41317,6 @@
       <c r="O233" t="n">
         <v>0</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0</v>
       </c>
@@ -42089,9 +41858,6 @@
       <c r="O236" t="n">
         <v>0</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0</v>
       </c>
@@ -42385,9 +42151,6 @@
       <c r="O238" t="n">
         <v>0</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0</v>
       </c>
@@ -42929,9 +42692,6 @@
       <c r="O241" t="n">
         <v>0</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0</v>
       </c>
@@ -43225,9 +42985,6 @@
       <c r="O243" t="n">
         <v>0</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0</v>
       </c>
@@ -43769,9 +43526,6 @@
       <c r="O246" t="n">
         <v>0</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0</v>
       </c>
@@ -44065,9 +43819,6 @@
       <c r="O248" t="n">
         <v>0</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0</v>
       </c>
@@ -44609,9 +44360,6 @@
       <c r="O251" t="n">
         <v>0</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0</v>
       </c>
@@ -44905,9 +44653,6 @@
       <c r="O253" t="n">
         <v>0</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>0</v>
       </c>
@@ -45449,9 +45194,6 @@
       <c r="O256" t="n">
         <v>0</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0</v>
       </c>
@@ -45745,9 +45487,6 @@
       <c r="O258" t="n">
         <v>0</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>0</v>
       </c>
@@ -46289,9 +46028,6 @@
       <c r="O261" t="n">
         <v>0</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="R261" t="n">
         <v>0</v>
       </c>
@@ -46585,9 +46321,6 @@
       <c r="O263" t="n">
         <v>0</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0</v>
       </c>
@@ -47129,9 +46862,6 @@
       <c r="O266" t="n">
         <v>0</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>0</v>
       </c>
@@ -47525,9 +47255,6 @@
       <c r="O268" t="n">
         <v>0</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0</v>
       </c>
@@ -47821,9 +47548,6 @@
       <c r="O270" t="n">
         <v>0</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0</v>
       </c>
@@ -48365,9 +48089,6 @@
       <c r="O273" t="n">
         <v>0</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0</v>
       </c>
@@ -48661,9 +48382,6 @@
       <c r="O275" t="n">
         <v>0</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0</v>
       </c>
@@ -49205,9 +48923,6 @@
       <c r="O278" t="n">
         <v>0</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0</v>
       </c>
@@ -49501,9 +49216,6 @@
       <c r="O280" t="n">
         <v>0</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0</v>
       </c>
@@ -50045,9 +49757,6 @@
       <c r="O283" t="n">
         <v>0</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0</v>
       </c>
@@ -50341,9 +50050,6 @@
       <c r="O285" t="n">
         <v>0</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0</v>
       </c>
@@ -50885,9 +50591,6 @@
       <c r="O288" t="n">
         <v>0</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0</v>
       </c>
@@ -51181,9 +50884,6 @@
       <c r="O290" t="n">
         <v>0</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0</v>
       </c>
@@ -51725,9 +51425,6 @@
       <c r="O293" t="n">
         <v>0</v>
       </c>
-      <c r="Q293" t="n">
-        <v>0</v>
-      </c>
       <c r="R293" t="n">
         <v>0</v>
       </c>
@@ -52021,9 +51718,6 @@
       <c r="O295" t="n">
         <v>0</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0</v>
       </c>
@@ -52565,9 +52259,6 @@
       <c r="O298" t="n">
         <v>0</v>
       </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
       <c r="R298" t="n">
         <v>0</v>
       </c>
@@ -52861,9 +52552,6 @@
       <c r="O300" t="n">
         <v>0</v>
       </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
       <c r="R300" t="n">
         <v>0</v>
       </c>
@@ -53405,9 +53093,6 @@
       <c r="O303" t="n">
         <v>0</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="R303" t="n">
         <v>0</v>
       </c>
@@ -53701,9 +53386,6 @@
       <c r="O305" t="n">
         <v>0</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>0</v>
       </c>
@@ -54245,9 +53927,6 @@
       <c r="O308" t="n">
         <v>0</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>0</v>
       </c>
@@ -54541,9 +54220,6 @@
       <c r="O310" t="n">
         <v>0</v>
       </c>
-      <c r="Q310" t="n">
-        <v>0</v>
-      </c>
       <c r="R310" t="n">
         <v>0</v>
       </c>
@@ -55085,9 +54761,6 @@
       <c r="O313" t="n">
         <v>0</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0</v>
       </c>
@@ -55381,9 +55054,6 @@
       <c r="O315" t="n">
         <v>0</v>
       </c>
-      <c r="Q315" t="n">
-        <v>0</v>
-      </c>
       <c r="R315" t="n">
         <v>0</v>
       </c>
@@ -55925,9 +55595,6 @@
       <c r="O318" t="n">
         <v>0</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="R318" t="n">
         <v>0</v>
       </c>
@@ -56221,9 +55888,6 @@
       <c r="O320" t="n">
         <v>0</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>0</v>
       </c>
@@ -56763,9 +56427,6 @@
         <v>0</v>
       </c>
       <c r="O323" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q323" t="n">
         <v>0</v>
       </c>
       <c r="R323" t="n">
